--- a/stories/arbres/ATOM-REL.CON.002-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, papa emmène Alice à l'école. Alice range son manteau. Dans le couloir, un camarade la bouscule. Alice sent son épaule. Elle dit : stop. Sa voix est claire. Puis Alice s'éloigne. Elle fait trois pas vers le mur. Elle va vers la maîtresse. La maîtresse écoute. Alice dit : j'ai dit stop. Je me suis éloignée. La maîtresse reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Alice dit encore : stop. Elle s'éloigne. Elle rejoint la maîtresse. Le soir, papa arrive. Alice raconte. Papa dit : tu as dit stop. Tu t'es éloignée. Tu as rejoint la maîtresse. Même leçon, autre moment.</t>
+          <t>Le matin, papa emmène Alice à l'école. Alice range son manteau. Dans le couloir, un camarade la bouscule. Alice sent son épaule. Stop. Sa voix est claire. Puis Alice s'éloigne. Elle fait trois pas vers le mur. Elle va vers la maîtresse. La maîtresse écoute. J'ai dit stop. Je me suis éloignée. La maîtresse reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Alice dit encore : stop. Elle s'éloigne. Elle rejoint la maîtresse. Le soir, papa arrive. Alice raconte. Tu as dit stop. Tu t'es éloignée. Tu as rejoint la maîtresse. Même leçon, autre moment.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, papa emmène Alice à l'école. Alice range son manteau. Dans le couloir, un camarade la bouscule. Alice sent son épaule.
+narrateur|Stop. Sa voix est claire.
+narrateur|Puis Alice s'éloigne. Elle fait trois pas vers le mur. Elle va vers la maîtresse. La maîtresse écoute.
+enfant-f|J'ai dit stop. Je me suis éloignée.
+narrateur|La maîtresse reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Alice dit encore : stop. Elle s'éloigne. Elle rejoint la maîtresse. Le soir, papa arrive. Alice raconte.
+papa|Tu as dit stop. Tu t'es éloignée. Tu as rejoint la maîtresse. Même leçon, autre moment.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Alice. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Alice a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Papa a écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Alice prend la main de papa. Ils marchent vers la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 papa|Tu as dit stop. Tu t'es éloignée. Tu as rejoint la maîtresse. Même leçon, autre moment.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Un camarade bouscule Alice. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Alice a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Papa a écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Alice prend la main de papa. Ils marchent vers la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.002-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alice dit stop et rejoint la maîtresse</t>
+          <t>Victorino dit stop dans le couloir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino range son manteau dans le couloir. Un camarade passe trop près, puis encore à la récréation. Il dit stop, s'éloigne, rejoint la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, papa emmène Alice à l'école. Alice range son manteau. Dans le couloir, un camarade la bouscule. Alice sent son épaule. Stop. Sa voix est claire. Puis Alice s'éloigne. Elle fait trois pas vers le mur. Elle va vers la maîtresse. La maîtresse écoute. J'ai dit stop. Je me suis éloignée. La maîtresse reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Alice dit encore : stop. Elle s'éloigne. Elle rejoint la maîtresse. Le soir, papa arrive. Alice raconte. Tu as dit stop. Tu t'es éloignée. Tu as rejoint la maîtresse. Même leçon, autre moment.</t>
+          <t>Les carreaux du couloir sont froids et lisses. Les chaussures font un petit écho. L'écho revient, tout mince. Une vitre est un peu embuée. Un doigt pourrait y dessiner un rond. Une lumière pâle passe à travers. Papa pose le cartable sous le crochet. Tu as vu la buée, Victorino ? Oui, papa. La vitre est floue. C'est le chaud du couloir. Je reviens ce soir. D'accord. En ce moment, Victorino range son manteau. Le manteau sent encore le dehors. La manche est un peu humide. Il sent la pluie. Victorino pousse le crochet. Le crochet tinte, tout court. Dans le couloir, un camarade passe trop près. Victorino sent son épaule. Son cœur tape. Stop. Sa voix est claire. Victorino fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Il marche vers la porte de la classe. On m'a bousculé. La maîtresse l'écoute. Victorino reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Victorino se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. J'ai dit stop. Je me suis éloigné. La maîtresse l'écoute encore. Victorino reste près d'elle. Il pose une main sur le mur du couloir. Le mur est lisse et un peu froid. Je reste ici. Victorino souffle. Son cœur tape moins vite. Le soir, papa arrive. La vitre n'est plus embuée. Victorino passe un doigt sur le verre. Le verre est lisse, maintenant. Tu as rangé ton manteau ? Oui. Dans le couloir, trop près. Puis à la récréation. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Victorino. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. C'est du bon travail. Même à la récréation ? Oui. Même leçon, autre moment. Oui, papa. Papa prend sa main. L'écho des chaussures redevient petit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le matin, papa emmène Alice à l'école. Alice range son manteau. Dans le couloir, un camarade la bouscule. Alice sent son épaule.
-narrateur|Stop. Sa voix est claire.
-narrateur|Puis Alice s'éloigne. Elle fait trois pas vers le mur. Elle va vers la maîtresse. La maîtresse écoute.
-enfant-f|J'ai dit stop. Je me suis éloignée.
-narrateur|La maîtresse reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Alice dit encore : stop. Elle s'éloigne. Elle rejoint la maîtresse. Le soir, papa arrive. Alice raconte.
-papa|Tu as dit stop. Tu t'es éloignée. Tu as rejoint la maîtresse. Même leçon, autre moment.</t>
+          <t>narrateur|Les carreaux du couloir sont froids et lisses.
+narrateur|Les chaussures font un petit écho.
+narrateur|L'écho revient, tout mince.
+narrateur|Une vitre est un peu embuée.
+narrateur|Un doigt pourrait y dessiner un rond.
+narrateur|Une lumière pâle passe à travers.
+narrateur|Papa pose le cartable sous le crochet.
+papa|Tu as vu la buée, Victorino ?
+enfant-m|Oui, papa.
+enfant-m|La vitre est floue.
+papa|C'est le chaud du couloir.
+papa|Je reviens ce soir.
+enfant-m|D'accord.
+narrateur|En ce moment, Victorino range son manteau.
+narrateur|Le manteau sent encore le dehors.
+narrateur|La manche est un peu humide.
+enfant-m|Il sent la pluie.
+narrateur|Victorino pousse le crochet.
+narrateur|Le crochet tinte, tout court.
+narrateur|Dans le couloir, un camarade passe trop près.
+narrateur|Victorino sent son épaule.
+narrateur|Son cœur tape.
+enfant-m|Stop.
+narrateur|Sa voix est claire.
+narrateur|Victorino fait un pas.
+narrateur|Il peut s'éloigner.
+narrateur|S'éloigner, c'est aller vers la maîtresse.
+narrateur|Il marche vers la porte de la classe.
+enfant-m|On m'a bousculé.
+narrateur|La maîtresse l'écoute.
+narrateur|Victorino reste près d'elle.
+narrateur|Plus tard, à la récréation, le camarade arrive trop près.
+narrateur|Victorino se souvient.
+enfant-m|Stop.
+narrateur|Il s'éloigne.
+narrateur|Il rejoint la maîtresse.
+enfant-m|J'ai dit stop.
+enfant-m|Je me suis éloigné.
+narrateur|La maîtresse l'écoute encore.
+narrateur|Victorino reste près d'elle.
+narrateur|Il pose une main sur le mur du couloir.
+narrateur|Le mur est lisse et un peu froid.
+enfant-m|Je reste ici.
+narrateur|Victorino souffle.
+narrateur|Son cœur tape moins vite.
+narrateur|Le soir, papa arrive.
+narrateur|La vitre n'est plus embuée.
+narrateur|Victorino passe un doigt sur le verre.
+narrateur|Le verre est lisse, maintenant.
+papa|Tu as rangé ton manteau ?
+enfant-m|Oui.
+enfant-m|Dans le couloir, trop près.
+enfant-m|Puis à la récréation.
+enfant-m|J'ai dit stop.
+enfant-m|Je suis allé vers la maîtresse.
+papa|Bravo, Victorino.
+papa|Tu as dit stop.
+papa|Tu t'es éloigné.
+papa|Tu as rejoint la maîtresse.
+papa|C'est du bon travail.
+papa|Même à la récréation ?
+enfant-m|Oui.
+papa|Même leçon, autre moment.
+enfant-m|Oui, papa.
+narrateur|Papa prend sa main.
+narrateur|L'écho des chaussures redevient petit.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1345,7 +1417,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Un camarade bouscule Alice. Que fait-elle ?</t>
+          <t>Un camarade bouscule Victorino. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade bouscule Alice. Que fait-elle ?</t>
+          <t>narrateur|Un camarade bouscule Victorino.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Alice a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Papa a écouté.</t>
+          <t>Victorino a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans le couloir, et après aussi. Stop, puis la maîtresse. Oui. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1746,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Alice a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Papa a écouté.</t>
+          <t>narrateur|Victorino a dit stop.
+narrateur|Il s'est éloigné.
+narrateur|Il a rejoint la maîtresse.
+papa|Bravo.
+papa|Dans le couloir, et après aussi.
+enfant-m|Stop, puis la maîtresse.
+papa|Oui.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Alice prend la main de papa. Ils marchent vers la maison.</t>
+          <t>Victorino prend la main de papa. On marche vers la maison ? Oui, papa. Les carreaux ne sonnent plus. Tu as encore un peu froid à l'épaule ? Non. La vitre est claire, maintenant. Oui. Le manteau pend, calme, sous le crochet. L'écho du couloir est parti. On ferme la porte du couloir ? Oui, papa. Les carreaux redeviennent silencieux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,7 +1921,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Alice prend la main de papa. Ils marchent vers la maison.</t>
+          <t>narrateur|Victorino prend la main de papa.
+papa|On marche vers la maison ?
+enfant-m|Oui, papa.
+narrateur|Les carreaux ne sonnent plus.
+papa|Tu as encore un peu froid à l'épaule ?
+enfant-m|Non.
+papa|La vitre est claire, maintenant.
+enfant-m|Oui.
+narrateur|Le manteau pend, calme, sous le crochet.
+narrateur|L'écho du couloir est parti.
+papa|On ferme la porte du couloir ?
+enfant-m|Oui, papa.
+narrateur|Les carreaux redeviennent silencieux.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1869,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Victorino. Tu as fait du bon travail. La vitre du couloir est claire, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,7 +2101,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit stop.
+enfant-m|Je suis allé vers la maîtresse.
+papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+narrateur|La vitre du couloir est claire, maintenant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2031,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2166,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les carreaux du couloir sont froids et lisses. Les chaussures font un petit écho. L'écho revient, tout mince. Une vitre est un peu embuée. Un doigt pourrait y dessiner un rond. Une lumière pâle passe à travers. Papa pose le cartable sous le crochet. Tu as vu la buée, Victorino ? Oui, papa. La vitre est floue. C'est le chaud du couloir. Je reviens ce soir. D'accord. En ce moment, Victorino range son manteau. Le manteau sent encore le dehors. La manche est un peu humide. Il sent la pluie. Victorino pousse le crochet. Le crochet tinte, tout court. Dans le couloir, un camarade passe trop près. Victorino sent son épaule. Son cœur tape. Stop. Sa voix est claire. Victorino fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Il marche vers la porte de la classe. On m'a bousculé. La maîtresse l'écoute. Victorino reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Victorino se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. J'ai dit stop. Je me suis éloigné. La maîtresse l'écoute encore. Victorino reste près d'elle. Il pose une main sur le mur du couloir. Le mur est lisse et un peu froid. Je reste ici. Victorino souffle. Son cœur tape moins vite. Le soir, papa arrive. La vitre n'est plus embuée. Victorino passe un doigt sur le verre. Le verre est lisse, maintenant. Tu as rangé ton manteau ? Oui. Dans le couloir, trop près. Puis à la récréation. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Victorino. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. C'est du bon travail. Même à la récréation ? Oui. Même leçon, autre moment. Oui, papa. Papa prend sa main. L'écho des chaussures redevient petit.</t>
+          <t>Les carreaux du couloir sont froids et lisses. Les chaussures font un petit écho. L'écho revient, tout mince. Une vitre est un peu embuée. Un doigt pourrait y dessiner un rond. Une lumière pâle passe à travers. Papa pose le cartable sous le crochet. Tu as vu la buée, Victorino ? Oui, papa. La vitre est floue. C'est le chaud du couloir. Je reviens ce soir. D'accord. En ce moment, Victorino range son manteau. Le manteau sent encore le dehors. La manche est un peu humide. Il sent la pluie. Victorino pousse le crochet. Le crochet tinte, tout court. Dans le couloir, un camarade passe trop près. Victorino sent son épaule. Son cœur tape. Stop. Sa voix est claire. Victorino fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Il marche vers la porte de la classe. On m'a bousculé. La maîtresse l'écoute. Victorino reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Victorino se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. J'ai dit stop. Je me suis éloigné. La maîtresse l'écoute encore. Victorino reste près d'elle. Il pose une main sur le mur du couloir. Le mur est lisse et un peu froid. Je reste ici. Victorino souffle. Son cœur tape moins vite. Le soir, papa arrive. La vitre n'est plus embuée. Victorino passe un doigt sur le verre. Le verre est lisse, maintenant. Tu as rangé ton manteau ? Oui. Dans le couloir, trop près. Puis à la récréation. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Victorino. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. Même à la récréation ? Oui. Même leçon, autre moment. Oui, papa. Papa prend sa main. L'écho des chaussures redevient petit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le matin, papa emmène Alice à l'école. Alice range son manteau. Dans le couloir, un camarade la bouscule. Alice sent son épaule. Elle dit : &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Sa voix est claire. Puis Alice s'éloigne. Elle fait trois pas vers le mur. Elle va vers la maîtresse. La maîtresse écoute. Alice dit : j'ai dit stop. Je me suis éloignée. La maîtresse reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Alice dit encore : stop. Elle s'éloigne. Elle rejoint la maîtresse. Le soir, papa arrive. Alice raconte. Papa dit : tu as dit stop. Tu t'es éloignée. Tu as rejoint la maîtresse. Même leçon, autre moment.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les carreaux du couloir sont froids et lisses. Les chaussures font un petit écho. L'écho revient, tout mince. Une vitre est un peu embuée. Un doigt pourrait y dessiner un rond. Une lumière pâle passe à travers. Papa pose le cartable sous le crochet. Tu as vu la buée, Victorino ? Oui, papa. La vitre est floue. C'est le chaud du couloir. Je reviens ce soir. D'accord. En ce moment, Victorino range son manteau. Le manteau sent encore le dehors. La manche est un peu humide. Il sent la pluie. Victorino pousse le crochet. Le crochet tinte, tout court. Dans le couloir, un camarade passe trop près. Victorino sent son épaule. Son cœur tape. Stop. Sa voix est claire. Victorino fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Il marche vers la porte de la classe. On m'a bousculé. La maîtresse l'écoute. Victorino reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Victorino se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. J'ai dit stop. Je me suis éloigné. La maîtresse l'écoute encore. Victorino reste près d'elle. Il pose une main sur le mur du couloir. Le mur est lisse et un peu froid. Je reste ici. Victorino souffle. Son cœur tape moins vite. Le soir, papa arrive. La vitre n'est plus embuée. Victorino passe un doigt sur le verre. Le verre est lisse, maintenant. Tu as rangé ton manteau ? Oui. Dans le couloir, trop près. Puis à la récréation. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Victorino. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. Même à la récréation ? Oui. Même leçon, autre moment. Oui, papa. Papa prend sa main. L'écho des chaussures redevient petit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1383,7 +1383,6 @@
 papa|Tu as dit stop.
 papa|Tu t'es éloigné.
 papa|Tu as rejoint la maîtresse.
-papa|C'est du bon travail.
 papa|Même à la récréation ?
 enfant-m|Oui.
 papa|Même leçon, autre moment.
@@ -1392,7 +1391,6 @@
 narrateur|L'écho des chaussures redevient petit.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1422,7 +1420,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un camarade bouscule Alice. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade bouscule Victorino. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1577,7 +1575,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1602,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans le couloir, et après aussi. Stop, puis la maîtresse. Oui. Tu as fait du bon travail.</t>
+          <t>Victorino a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans le couloir, et après aussi. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Alice a dit &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Elle s'est éloignée. Elle a rejoint la maîtresse. Papa a écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans le couloir, et après aussi. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1752,11 +1749,9 @@
 papa|Bravo.
 papa|Dans le couloir, et après aussi.
 enfant-m|Stop, puis la maîtresse.
-papa|Oui.
-papa|Tu as fait du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+papa|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1786,7 +1781,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Alice prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils marchent vers la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino prend la main de papa. On marche vers la maison ? Oui, papa. Les carreaux ne sonnent plus. Tu as encore un peu froid à l'épaule ? Non. La vitre est claire, maintenant. Oui. Le manteau pend, calme, sous le crochet. L'écho du couloir est parti. On ferme la porte du couloir ? Oui, papa. Les carreaux redeviennent silencieux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1936,7 +1931,6 @@
 narrateur|Les carreaux redeviennent silencieux.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Victorino. Tu as fait du bon travail. La vitre du couloir est claire, maintenant. L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Victorino. La vitre du couloir est claire, maintenant.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Victorino. La vitre du couloir est claire, maintenant.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,12 +2098,9 @@
           <t>enfant-m|J'ai dit stop.
 enfant-m|Je suis allé vers la maîtresse.
 papa|Bravo, Victorino.
-papa|Tu as fait du bon travail.
-narrateur|La vitre du couloir est claire, maintenant.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La vitre du couloir est claire, maintenant.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2128,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alice, maîtresse, papa</t>
+          <t>Victorino, maîtresse, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-07.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Victorino dit stop dans le couloir</t>
+          <t>La buée du couloir</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école, couloir</t>
+          <t>école, couloir embué, récréation</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Victorino, maîtresse, papa</t>
+          <t>Victorino, Aniss, papa</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Victorino range son manteau dans le couloir. Un camarade passe trop près, puis encore à la récréation. Il dit stop, s'éloigne, rejoint la maîtresse.</t>
+          <t>Victorino veut accrocher son manteau mouillé au crochet du bateau. Aniss passe trop près dans le couloir. Stop, porte de la classe. À la récréation, près du soleil peint, Aniss trop près encore. Stop, mur. Le soir, la vitre est claire.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les carreaux du couloir sont froids et lisses. Les chaussures font un petit écho. L'écho revient, tout mince. Une vitre est un peu embuée. Un doigt pourrait y dessiner un rond. Une lumière pâle passe à travers. Papa pose le cartable sous le crochet. Tu as vu la buée, Victorino ? Oui, papa. La vitre est floue. C'est le chaud du couloir. Je reviens ce soir. D'accord. En ce moment, Victorino range son manteau. Le manteau sent encore le dehors. La manche est un peu humide. Il sent la pluie. Victorino pousse le crochet. Le crochet tinte, tout court. Dans le couloir, un camarade passe trop près. Victorino sent son épaule. Son cœur tape. Stop. Sa voix est claire. Victorino fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Il marche vers la porte de la classe. On m'a bousculé. La maîtresse l'écoute. Victorino reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Victorino se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. J'ai dit stop. Je me suis éloigné. La maîtresse l'écoute encore. Victorino reste près d'elle. Il pose une main sur le mur du couloir. Le mur est lisse et un peu froid. Je reste ici. Victorino souffle. Son cœur tape moins vite. Le soir, papa arrive. La vitre n'est plus embuée. Victorino passe un doigt sur le verre. Le verre est lisse, maintenant. Tu as rangé ton manteau ? Oui. Dans le couloir, trop près. Puis à la récréation. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Victorino. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. Même à la récréation ? Oui. Même leçon, autre moment. Oui, papa. Papa prend sa main. L'écho des chaussures redevient petit.</t>
+          <t>Une buée ronde tient sur la vitre du couloir. Les carreaux sont froids et lisses. Les chaussures font un petit écho. L'écho revient, tout mince. Une lumière pâle passe à travers la buée. Papa pose le cartable sous le crochet. Tu as vu la buée, Victorino ? Oui, papa. La vitre est floue. C'est le chaud du couloir. Je reviens ce soir. D'accord. Papa part vers la porte. En ce moment, Victorino range son manteau. Le manteau sent encore la pluie. La manche est un peu humide. Je veux le crochet du bateau. Un petit bateau est collé au bois. Victorino pousse le crochet. Le crochet tinte, tout court. Aniss arrive dans le couloir. Aniss passe trop près de l'épaule. Victorino sent le choc. Son cœur tape. Stop. Sa voix est claire. Il fait un pas vers la classe. Ses chaussures sonnent sur les carreaux. Il marche jusqu'à la porte. Aniss est passé trop près. La maîtresse l'écoute. Victorino reste près d'elle. Il pose une main sur le montant. Le bois est lisse et un peu froid. Je reste ici. Le manteau pend, calme, sous le bateau. Victorino souffle. Son cœur tape moins vite. Plus tard, la cloche sonne. La cour sent l'herbe mouillée. Un soleil jaune est peint sur le mur. Victorino veut poser une pomme de pin au pied. Elle va là, près du soleil. La pomme de pin est rêche sous les doigts. Il s'accroupit près du mur. Aniss arrive trop près encore. La pomme de pin roule. Victorino sent son épaule. Stop. Il fait un pas. La maîtresse est près du mur, maintenant. Victorino marche vers elle. Le soleil peint reste derrière. Encore trop près. La maîtresse l'écoute encore. Victorino reste près d'elle. Il pose une main sur le mur. Le mur est lisse et un peu froid. Je reste ici. Il souffle. La pomme de pin attend dans l'herbe. Le soir, papa arrive. La vitre n'est plus embuée. Victorino passe un doigt sur le verre. Le verre est lisse, maintenant. Tu as rangé ton manteau ? Oui. Au crochet du bateau. Aniss trop près, dans le couloir. Puis près du soleil peint. J'ai dit stop. Je suis allé vers la maîtresse. Dans le couloir ? Oui. Et dans la cour ? Stop encore. Bravo, Victorino. Tu es allé près d'elle. Oui, papa. Papa prend sa main. L'écho des chaussures redevient petit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Les carreaux du couloir sont froids et lisses. Les chaussures font un petit écho. L'écho revient, tout mince. Une vitre est un peu embuée. Un doigt pourrait y dessiner un rond. Une lumière pâle passe à travers. Papa pose le cartable sous le crochet. Tu as vu la buée, Victorino ? Oui, papa. La vitre est floue. C'est le chaud du couloir. Je reviens ce soir. D'accord. En ce moment, Victorino range son manteau. Le manteau sent encore le dehors. La manche est un peu humide. Il sent la pluie. Victorino pousse le crochet. Le crochet tinte, tout court. Dans le couloir, un camarade passe trop près. Victorino sent son épaule. Son cœur tape. Stop. Sa voix est claire. Victorino fait un pas. Il peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Il marche vers la porte de la classe. On m'a bousculé. La maîtresse l'écoute. Victorino reste près d'elle. Plus tard, à la récréation, le camarade arrive trop près. Victorino se souvient. Stop. Il s'éloigne. Il rejoint la maîtresse. J'ai dit stop. Je me suis éloigné. La maîtresse l'écoute encore. Victorino reste près d'elle. Il pose une main sur le mur du couloir. Le mur est lisse et un peu froid. Je reste ici. Victorino souffle. Son cœur tape moins vite. Le soir, papa arrive. La vitre n'est plus embuée. Victorino passe un doigt sur le verre. Le verre est lisse, maintenant. Tu as rangé ton manteau ? Oui. Dans le couloir, trop près. Puis à la récréation. J'ai dit stop. Je suis allé vers la maîtresse. Bravo, Victorino. Tu as dit stop. Tu t'es éloigné. Tu as rejoint la maîtresse. Même à la récréation ? Oui. Même leçon, autre moment. Oui, papa. Papa prend sa main. L'écho des chaussures redevient petit.</t>
+          <t>Une buée ronde tient sur la vitre du couloir. Les carreaux sont froids et lisses. Les chaussures font un petit écho. L'écho revient, tout mince. Une lumière pâle passe à travers la buée. Papa pose le cartable sous le crochet. Tu as vu la buée, Victorino ? Oui, papa. La vitre est floue. C'est le chaud du couloir. Je reviens ce soir. D'accord. Papa part vers la porte. En ce moment, Victorino range son manteau. Le manteau sent encore la pluie. La manche est un peu humide. Je veux le crochet du bateau. Un petit bateau est collé au bois. Victorino pousse le crochet. Le crochet tinte, tout court. Aniss arrive dans le couloir. Aniss passe trop près de l'épaule. Victorino sent le choc. Son cœur tape. Stop. Sa voix est claire. Il fait un pas vers la classe. Ses chaussures sonnent sur les carreaux. Il marche jusqu'à la porte. Aniss est passé trop près. La maîtresse l'écoute. Victorino reste près d'elle. Il pose une main sur le montant. Le bois est lisse et un peu froid. Je reste ici. Le manteau pend, calme, sous le bateau. Victorino souffle. Son cœur tape moins vite. Plus tard, la cloche sonne. La cour sent l'herbe mouillée. Un soleil jaune est peint sur le mur. Victorino veut poser une pomme de pin au pied. Elle va là, près du soleil. La pomme de pin est rêche sous les doigts. Il s'accroupit près du mur. Aniss arrive trop près encore. La pomme de pin roule. Victorino sent son épaule. Stop. Il fait un pas. La maîtresse est près du mur, maintenant. Victorino marche vers elle. Le soleil peint reste derrière. Encore trop près. La maîtresse l'écoute encore. Victorino reste près d'elle. Il pose une main sur le mur. Le mur est lisse et un peu froid. Je reste ici. Il souffle. La pomme de pin attend dans l'herbe. Le soir, papa arrive. La vitre n'est plus embuée. Victorino passe un doigt sur le verre. Le verre est lisse, maintenant. Tu as rangé ton manteau ? Oui. Au crochet du bateau. Aniss trop près, dans le couloir. Puis près du soleil peint. J'ai dit stop. Je suis allé vers la maîtresse. Dans le couloir ? Oui. Et dans la cour ? Stop encore. Bravo, Victorino. Tu es allé près d'elle. Oui, papa. Papa prend sa main. L'écho des chaussures redevient petit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,12 +1324,11 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les carreaux du couloir sont froids et lisses.
+          <t>narrateur|Une buée ronde tient sur la vitre du couloir.
+narrateur|Les carreaux sont froids et lisses.
 narrateur|Les chaussures font un petit écho.
 narrateur|L'écho revient, tout mince.
-narrateur|Une vitre est un peu embuée.
-narrateur|Un doigt pourrait y dessiner un rond.
-narrateur|Une lumière pâle passe à travers.
+narrateur|Une lumière pâle passe à travers la buée.
 narrateur|Papa pose le cartable sous le crochet.
 papa|Tu as vu la buée, Victorino ?
 enfant-m|Oui, papa.
@@ -1337,55 +1336,72 @@
 papa|C'est le chaud du couloir.
 papa|Je reviens ce soir.
 enfant-m|D'accord.
+narrateur|Papa part vers la porte.
 narrateur|En ce moment, Victorino range son manteau.
-narrateur|Le manteau sent encore le dehors.
+narrateur|Le manteau sent encore la pluie.
 narrateur|La manche est un peu humide.
-enfant-m|Il sent la pluie.
+enfant-m|Je veux le crochet du bateau.
+narrateur|Un petit bateau est collé au bois.
 narrateur|Victorino pousse le crochet.
 narrateur|Le crochet tinte, tout court.
-narrateur|Dans le couloir, un camarade passe trop près.
-narrateur|Victorino sent son épaule.
+narrateur|Aniss arrive dans le couloir.
+narrateur|Aniss passe trop près de l'épaule.
+narrateur|Victorino sent le choc.
 narrateur|Son cœur tape.
 enfant-m|Stop.
 narrateur|Sa voix est claire.
-narrateur|Victorino fait un pas.
-narrateur|Il peut s'éloigner.
-narrateur|S'éloigner, c'est aller vers la maîtresse.
-narrateur|Il marche vers la porte de la classe.
-enfant-m|On m'a bousculé.
+narrateur|Il fait un pas vers la classe.
+narrateur|Ses chaussures sonnent sur les carreaux.
+narrateur|Il marche jusqu'à la porte.
+enfant-m|Aniss est passé trop près.
 narrateur|La maîtresse l'écoute.
 narrateur|Victorino reste près d'elle.
-narrateur|Plus tard, à la récréation, le camarade arrive trop près.
-narrateur|Victorino se souvient.
+narrateur|Il pose une main sur le montant.
+narrateur|Le bois est lisse et un peu froid.
+enfant-m|Je reste ici.
+narrateur|Le manteau pend, calme, sous le bateau.
+narrateur|Victorino souffle.
+narrateur|Son cœur tape moins vite.
+narrateur|Plus tard, la cloche sonne.
+narrateur|La cour sent l'herbe mouillée.
+narrateur|Un soleil jaune est peint sur le mur.
+narrateur|Victorino veut poser une pomme de pin au pied.
+enfant-m|Elle va là, près du soleil.
+narrateur|La pomme de pin est rêche sous les doigts.
+narrateur|Il s'accroupit près du mur.
+narrateur|Aniss arrive trop près encore.
+narrateur|La pomme de pin roule.
+narrateur|Victorino sent son épaule.
 enfant-m|Stop.
-narrateur|Il s'éloigne.
-narrateur|Il rejoint la maîtresse.
-enfant-m|J'ai dit stop.
-enfant-m|Je me suis éloigné.
+narrateur|Il fait un pas.
+narrateur|La maîtresse est près du mur, maintenant.
+narrateur|Victorino marche vers elle.
+narrateur|Le soleil peint reste derrière.
+enfant-m|Encore trop près.
 narrateur|La maîtresse l'écoute encore.
 narrateur|Victorino reste près d'elle.
-narrateur|Il pose une main sur le mur du couloir.
+narrateur|Il pose une main sur le mur.
 narrateur|Le mur est lisse et un peu froid.
 enfant-m|Je reste ici.
-narrateur|Victorino souffle.
-narrateur|Son cœur tape moins vite.
+narrateur|Il souffle.
+narrateur|La pomme de pin attend dans l'herbe.
 narrateur|Le soir, papa arrive.
 narrateur|La vitre n'est plus embuée.
 narrateur|Victorino passe un doigt sur le verre.
 narrateur|Le verre est lisse, maintenant.
 papa|Tu as rangé ton manteau ?
 enfant-m|Oui.
-enfant-m|Dans le couloir, trop près.
-enfant-m|Puis à la récréation.
+enfant-m|Au crochet du bateau.
+enfant-m|Aniss trop près, dans le couloir.
+enfant-m|Puis près du soleil peint.
 enfant-m|J'ai dit stop.
 enfant-m|Je suis allé vers la maîtresse.
+papa|Dans le couloir ?
+enfant-m|Oui.
+papa|Et dans la cour ?
+enfant-m|Stop encore.
 papa|Bravo, Victorino.
-papa|Tu as dit stop.
-papa|Tu t'es éloigné.
-papa|Tu as rejoint la maîtresse.
-papa|Même à la récréation ?
-enfant-m|Oui.
-papa|Même leçon, autre moment.
+papa|Tu es allé près d'elle.
 enfant-m|Oui, papa.
 narrateur|Papa prend sa main.
 narrateur|L'écho des chaussures redevient petit.</t>
@@ -1435,7 +1451,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>stop | elle dit stop | s'éloigner | elle s'éloigne | maîtresse | la maîtresse</t>
+          <t>stop | il dit stop | s'éloigner | maîtresse | vers la maîtresse</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1450,7 +1466,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle dit stop. Elle s'éloigne. Vers qui va-t-elle ?</t>
+          <t>Il dit stop. Il s'éloigne. Vers qui va-t-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1492,14 +1508,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1599,12 +1615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans le couloir, et après aussi. Stop, puis la maîtresse. Oui.</t>
+          <t>Victorino a dit stop. Il a fait un pas. Il a rejoint la maîtresse. Bravo. Dans le couloir, et près du mur. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a dit stop. Il s'est éloigné. Il a rejoint la maîtresse. Bravo. Dans le couloir, et après aussi. Stop, puis la maîtresse. Oui.</t>
+          <t>Victorino a dit stop. Il a fait un pas. Il a rejoint la maîtresse. Bravo. Dans le couloir, et près du mur. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1667,7 +1683,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1744,10 +1760,10 @@
       <c r="AW4" t="inlineStr">
         <is>
           <t>narrateur|Victorino a dit stop.
-narrateur|Il s'est éloigné.
+narrateur|Il a fait un pas.
 narrateur|Il a rejoint la maîtresse.
 papa|Bravo.
-papa|Dans le couloir, et après aussi.
+papa|Dans le couloir, et près du mur.
 enfant-m|Stop, puis la maîtresse.
 papa|Oui.</t>
         </is>
@@ -1776,12 +1792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorino prend la main de papa. On marche vers la maison ? Oui, papa. Les carreaux ne sonnent plus. Tu as encore un peu froid à l'épaule ? Non. La vitre est claire, maintenant. Oui. Le manteau pend, calme, sous le crochet. L'écho du couloir est parti. On ferme la porte du couloir ? Oui, papa. Les carreaux redeviennent silencieux.</t>
+          <t>Victorino prend la main de papa. On marche vers la maison ? Oui, papa. Les carreaux ne sonnent plus. Tu as encore un peu froid à l'épaule ? Non. La vitre est claire, maintenant ? Oui. Le manteau pend, calme, sous le crochet. On ferme la porte du couloir ? Oui, papa. Les carreaux redeviennent silencieux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Victorino prend la main de papa. On marche vers la maison ? Oui, papa. Les carreaux ne sonnent plus. Tu as encore un peu froid à l'épaule ? Non. La vitre est claire, maintenant. Oui. Le manteau pend, calme, sous le crochet. L'écho du couloir est parti. On ferme la porte du couloir ? Oui, papa. Les carreaux redeviennent silencieux.</t>
+          <t>Victorino prend la main de papa. On marche vers la maison ? Oui, papa. Les carreaux ne sonnent plus. Tu as encore un peu froid à l'épaule ? Non. La vitre est claire, maintenant ? Oui. Le manteau pend, calme, sous le crochet. On ferme la porte du couloir ? Oui, papa. Les carreaux redeviennent silencieux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1844,7 +1860,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1922,10 +1938,9 @@
 narrateur|Les carreaux ne sonnent plus.
 papa|Tu as encore un peu froid à l'épaule ?
 enfant-m|Non.
-papa|La vitre est claire, maintenant.
+papa|La vitre est claire, maintenant ?
 enfant-m|Oui.
 narrateur|Le manteau pend, calme, sous le crochet.
-narrateur|L'écho du couloir est parti.
 papa|On ferme la porte du couloir ?
 enfant-m|Oui, papa.
 narrateur|Les carreaux redeviennent silencieux.</t>
@@ -2023,7 +2038,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2119,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2184,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
